--- a/Flow/202609/2026-09-25/AIDPC_アウトプットファイル設計/input/対象患者リスト（退院日付き）.xlsx
+++ b/Flow/202609/2026-09-25/AIDPC_アウトプットファイル設計/input/対象患者リスト（退院日付き）.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ein.ad.sk-kumamoto.jp\管理部門\経営企画部\経営企画室\パブリック\中村主任へ（藤島より）\対象患者データ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juny4\Desktop\appl\git\aipm_v0\Flow\202609\2026-09-25\AIDPC_アウトプットファイル設計\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91ADFC9F-9A17-4D8E-8B9A-981264CF9655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="6852" yWindow="3228" windowWidth="24984" windowHeight="14400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="患者リスト" sheetId="1" r:id="rId1"/>
@@ -22,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>患者番号</t>
   </si>
@@ -55,12 +45,26 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>DPCコード14桁</t>
+    <rPh sb="8" eb="9">
+      <t>ケタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>点数</t>
+    <rPh sb="0" eb="2">
+      <t>テンスウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,6 +77,22 @@
       <sz val="6"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -99,13 +119,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -385,14 +406,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C692"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E692"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -402,8 +423,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>26890</v>
       </c>
@@ -414,7 +441,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>36548</v>
       </c>
@@ -425,7 +452,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>59495</v>
       </c>
@@ -436,7 +463,7 @@
         <v>46020</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>103060</v>
       </c>
@@ -447,7 +474,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>152316</v>
       </c>
@@ -458,7 +485,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>182333</v>
       </c>
@@ -469,7 +496,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>185822</v>
       </c>
@@ -480,7 +507,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>191724</v>
       </c>
@@ -491,7 +518,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>198398</v>
       </c>
@@ -502,7 +529,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>217504</v>
       </c>
@@ -513,7 +540,7 @@
         <v>45948</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>224181</v>
       </c>
@@ -524,7 +551,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>238180</v>
       </c>
@@ -535,7 +562,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>242987</v>
       </c>
@@ -546,7 +573,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>331974</v>
       </c>
@@ -557,7 +584,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>375332</v>
       </c>
@@ -568,7 +595,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>433831</v>
       </c>
@@ -579,7 +606,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>433831</v>
       </c>
@@ -590,7 +617,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>445139</v>
       </c>
@@ -601,7 +628,7 @@
         <v>45954</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>450255</v>
       </c>
@@ -612,7 +639,7 @@
         <v>46233</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>476451</v>
       </c>
@@ -623,7 +650,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>485614</v>
       </c>
@@ -634,7 +661,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>505175</v>
       </c>
@@ -645,7 +672,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>507535</v>
       </c>
@@ -656,7 +683,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>509363</v>
       </c>
@@ -667,7 +694,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>539544</v>
       </c>
@@ -678,7 +705,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>586858</v>
       </c>
@@ -689,7 +716,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>605595</v>
       </c>
@@ -700,7 +727,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>629014</v>
       </c>
@@ -711,7 +738,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>630500</v>
       </c>
@@ -722,7 +749,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>659257</v>
       </c>
@@ -733,7 +760,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>681216</v>
       </c>
@@ -744,7 +771,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>681519</v>
       </c>
@@ -755,7 +782,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>692435</v>
       </c>
@@ -766,7 +793,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>702844</v>
       </c>
@@ -777,7 +804,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>865177</v>
       </c>
@@ -788,7 +815,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>882553</v>
       </c>
@@ -799,7 +826,7 @@
         <v>45965</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>917128</v>
       </c>
@@ -810,7 +837,7 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>940367</v>
       </c>
@@ -821,7 +848,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>955798</v>
       </c>
@@ -832,7 +859,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>960395</v>
       </c>
@@ -843,7 +870,7 @@
         <v>45993</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>965496</v>
       </c>
@@ -854,7 +881,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>978328</v>
       </c>
@@ -865,7 +892,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>980549</v>
       </c>
@@ -876,7 +903,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>988773</v>
       </c>
@@ -887,7 +914,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>1204522</v>
       </c>
@@ -898,7 +925,7 @@
         <v>46004</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>1211072</v>
       </c>
@@ -909,7 +936,7 @@
         <v>46179</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>1276220</v>
       </c>
@@ -920,7 +947,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>1323714</v>
       </c>
@@ -931,7 +958,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>1350177</v>
       </c>
@@ -942,7 +969,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>1372983</v>
       </c>
@@ -953,7 +980,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>1409766</v>
       </c>
@@ -964,7 +991,7 @@
         <v>45966</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>1413551</v>
       </c>
@@ -975,7 +1002,7 @@
         <v>45973</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>1416987</v>
       </c>
@@ -986,7 +1013,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>1423350</v>
       </c>
@@ -997,7 +1024,7 @@
         <v>45993</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>1436977</v>
       </c>
@@ -1008,7 +1035,7 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>1446853</v>
       </c>
@@ -1019,7 +1046,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>1449760</v>
       </c>
@@ -1030,7 +1057,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>1457539</v>
       </c>
@@ -1041,7 +1068,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>1459393</v>
       </c>
@@ -1052,7 +1079,7 @@
         <v>46021</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>1460839</v>
       </c>
@@ -1063,7 +1090,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>1461413</v>
       </c>
@@ -1074,7 +1101,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>1474662</v>
       </c>
@@ -1085,7 +1112,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>1516953</v>
       </c>
@@ -1096,7 +1123,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>1518399</v>
       </c>
@@ -1107,7 +1134,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>1554496</v>
       </c>
@@ -1118,7 +1145,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>1573181</v>
       </c>
@@ -1129,7 +1156,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>1591191</v>
       </c>
@@ -1140,7 +1167,7 @@
         <v>45942</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>1595024</v>
       </c>
@@ -1151,7 +1178,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>1597345</v>
       </c>
@@ -1162,7 +1189,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>1635133</v>
       </c>
@@ -1173,7 +1200,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>1638228</v>
       </c>
@@ -1184,7 +1211,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>1638228</v>
       </c>
@@ -1195,7 +1222,7 @@
         <v>46207</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>1653496</v>
       </c>
@@ -1206,7 +1233,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>1660148</v>
       </c>
@@ -1217,7 +1244,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>1667142</v>
       </c>
@@ -1228,7 +1255,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>1690595</v>
       </c>
@@ -1239,7 +1266,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>1695103</v>
       </c>
@@ -1250,7 +1277,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>1696953</v>
       </c>
@@ -1261,7 +1288,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>1712288</v>
       </c>
@@ -1272,7 +1299,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>1730159</v>
       </c>
@@ -1283,7 +1310,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>1754844</v>
       </c>
@@ -1294,7 +1321,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>1763829</v>
       </c>
@@ -1305,7 +1332,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>1797008</v>
       </c>
@@ -1316,7 +1343,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>1821001</v>
       </c>
@@ -1327,7 +1354,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1821847</v>
       </c>
@@ -1338,7 +1365,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>1828865</v>
       </c>
@@ -1349,7 +1376,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>1842372</v>
       </c>
@@ -1360,7 +1387,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>1857943</v>
       </c>
@@ -1371,7 +1398,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>1887578</v>
       </c>
@@ -1382,7 +1409,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1893230</v>
       </c>
@@ -1393,7 +1420,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1927079</v>
       </c>
@@ -1404,7 +1431,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1970335</v>
       </c>
@@ -1415,7 +1442,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>1983255</v>
       </c>
@@ -1426,7 +1453,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>1999208</v>
       </c>
@@ -1437,7 +1464,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>2005064</v>
       </c>
@@ -1448,7 +1475,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>2010988</v>
       </c>
@@ -1459,7 +1486,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>2026121</v>
       </c>
@@ -1470,7 +1497,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>2032388</v>
       </c>
@@ -1481,7 +1508,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>2035106</v>
       </c>
@@ -1492,7 +1519,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>2040246</v>
       </c>
@@ -1503,7 +1530,7 @@
         <v>46013</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>2045501</v>
       </c>
@@ -1514,7 +1541,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>2049282</v>
       </c>
@@ -1525,7 +1552,7 @@
         <v>46233</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>2087725</v>
       </c>
@@ -1536,7 +1563,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>2146062</v>
       </c>
@@ -1547,7 +1574,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>2146062</v>
       </c>
@@ -1558,7 +1585,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>2188781</v>
       </c>
@@ -1569,7 +1596,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>2212176</v>
       </c>
@@ -1580,7 +1607,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>2255443</v>
       </c>
@@ -1591,7 +1618,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>2279974</v>
       </c>
@@ -1602,7 +1629,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>2290601</v>
       </c>
@@ -1613,7 +1640,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>2297275</v>
       </c>
@@ -1624,7 +1651,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>2305250</v>
       </c>
@@ -1635,7 +1662,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>2340052</v>
       </c>
@@ -1646,7 +1673,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>2344226</v>
       </c>
@@ -1657,7 +1684,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>2420963</v>
       </c>
@@ -1668,7 +1695,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>2467909</v>
       </c>
@@ -1679,7 +1706,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>2478128</v>
       </c>
@@ -1690,7 +1717,7 @@
         <v>45950</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>2488131</v>
       </c>
@@ -1701,7 +1728,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>2489715</v>
       </c>
@@ -1712,7 +1739,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>2492786</v>
       </c>
@@ -1723,7 +1750,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>2508604</v>
       </c>
@@ -1734,7 +1761,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>2530928</v>
       </c>
@@ -1745,7 +1772,7 @@
         <v>45998</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>2533657</v>
       </c>
@@ -1756,7 +1783,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>2537085</v>
       </c>
@@ -1767,7 +1794,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>2560844</v>
       </c>
@@ -1778,7 +1805,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>2581999</v>
       </c>
@@ -1789,7 +1816,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>2581999</v>
       </c>
@@ -1800,7 +1827,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>2587989</v>
       </c>
@@ -1811,7 +1838,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>2589527</v>
       </c>
@@ -1822,7 +1849,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>2597512</v>
       </c>
@@ -1833,7 +1860,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>2617871</v>
       </c>
@@ -1844,7 +1871,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>2623862</v>
       </c>
@@ -1855,7 +1882,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>2633370</v>
       </c>
@@ -1866,7 +1893,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>2638813</v>
       </c>
@@ -1877,7 +1904,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>2652015</v>
       </c>
@@ -1888,7 +1915,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>2654970</v>
       </c>
@@ -1899,7 +1926,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>2688123</v>
       </c>
@@ -1910,7 +1937,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>2690039</v>
       </c>
@@ -1921,7 +1948,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>2717114</v>
       </c>
@@ -1932,7 +1959,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>2718320</v>
       </c>
@@ -1943,7 +1970,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>2727963</v>
       </c>
@@ -1954,7 +1981,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>2754542</v>
       </c>
@@ -1965,7 +1992,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>2783810</v>
       </c>
@@ -1976,7 +2003,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>2786082</v>
       </c>
@@ -1987,7 +2014,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>2788187</v>
       </c>
@@ -1998,7 +2025,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>2801810</v>
       </c>
@@ -2009,7 +2036,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>2803129</v>
       </c>
@@ -2020,7 +2047,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>2803713</v>
       </c>
@@ -2031,7 +2058,7 @@
         <v>46141</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>2821634</v>
       </c>
@@ -2042,7 +2069,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>2825098</v>
       </c>
@@ -2053,7 +2080,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>2862933</v>
       </c>
@@ -2064,7 +2091,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>2863062</v>
       </c>
@@ -2075,7 +2102,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>2882175</v>
       </c>
@@ -2086,7 +2113,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>2907016</v>
       </c>
@@ -2097,7 +2124,7 @@
         <v>45993</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>2907016</v>
       </c>
@@ -2108,7 +2135,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>2915405</v>
       </c>
@@ -2119,7 +2146,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>2921965</v>
       </c>
@@ -2130,7 +2157,7 @@
         <v>45994</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>2925696</v>
       </c>
@@ -2141,7 +2168,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>2943199</v>
       </c>
@@ -2152,7 +2179,7 @@
         <v>46002</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>2959572</v>
       </c>
@@ -2163,7 +2190,7 @@
         <v>46233</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>2960032</v>
       </c>
@@ -2174,7 +2201,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>2984753</v>
       </c>
@@ -2185,7 +2212,7 @@
         <v>46002</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>2984892</v>
       </c>
@@ -2196,7 +2223,7 @@
         <v>46211</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>2986062</v>
       </c>
@@ -2207,7 +2234,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>3023001</v>
       </c>
@@ -2218,7 +2245,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>3024546</v>
       </c>
@@ -2229,7 +2256,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>3035715</v>
       </c>
@@ -2240,7 +2267,7 @@
         <v>46044</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>3039814</v>
       </c>
@@ -2251,7 +2278,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>3046984</v>
       </c>
@@ -2262,7 +2289,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>3065352</v>
       </c>
@@ -2273,7 +2300,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>3072179</v>
       </c>
@@ -2284,7 +2311,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>3097739</v>
       </c>
@@ -2295,7 +2322,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>3107908</v>
       </c>
@@ -2306,7 +2333,7 @@
         <v>45999</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>3108962</v>
       </c>
@@ -2317,7 +2344,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>3122518</v>
       </c>
@@ -2328,7 +2355,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>3131543</v>
       </c>
@@ -2339,7 +2366,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>3132975</v>
       </c>
@@ -2350,7 +2377,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>3136997</v>
       </c>
@@ -2361,7 +2388,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>3152193</v>
       </c>
@@ -2372,7 +2399,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>3154844</v>
       </c>
@@ -2383,7 +2410,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>3158575</v>
       </c>
@@ -2394,7 +2421,7 @@
         <v>45948</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>3184126</v>
       </c>
@@ -2405,7 +2432,7 @@
         <v>46018</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>3190434</v>
       </c>
@@ -2416,7 +2443,7 @@
         <v>46020</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>3197022</v>
       </c>
@@ -2427,7 +2454,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>3210262</v>
       </c>
@@ -2438,7 +2465,7 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>3210402</v>
       </c>
@@ -2449,7 +2476,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>3215983</v>
       </c>
@@ -2460,7 +2487,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>3216012</v>
       </c>
@@ -2471,7 +2498,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>3230125</v>
       </c>
@@ -2482,7 +2509,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>3289279</v>
       </c>
@@ -2493,7 +2520,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>3289926</v>
       </c>
@@ -2504,7 +2531,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>3306936</v>
       </c>
@@ -2515,7 +2542,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>3315694</v>
       </c>
@@ -2526,7 +2553,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>3333248</v>
       </c>
@@ -2537,7 +2564,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>3339353</v>
       </c>
@@ -2548,7 +2575,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>3351234</v>
       </c>
@@ -2559,7 +2586,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>3353909</v>
       </c>
@@ -2570,7 +2597,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>3354773</v>
       </c>
@@ -2581,7 +2608,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>3381631</v>
       </c>
@@ -2592,7 +2619,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>3389308</v>
       </c>
@@ -2603,7 +2630,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>3410723</v>
       </c>
@@ -2614,7 +2641,7 @@
         <v>45953</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>3419860</v>
       </c>
@@ -2625,7 +2652,7 @@
         <v>45988</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>3422982</v>
       </c>
@@ -2636,7 +2663,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>3457252</v>
       </c>
@@ -2647,7 +2674,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>3459357</v>
       </c>
@@ -2658,7 +2685,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>3467289</v>
       </c>
@@ -2669,7 +2696,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>3485566</v>
       </c>
@@ -2680,7 +2707,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>3501372</v>
       </c>
@@ -2691,7 +2718,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>3502564</v>
       </c>
@@ -2702,7 +2729,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>3519103</v>
       </c>
@@ -2713,7 +2740,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>3525233</v>
       </c>
@@ -2724,7 +2751,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>3526247</v>
       </c>
@@ -2735,7 +2762,7 @@
         <v>46011</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>3554056</v>
       </c>
@@ -2746,7 +2773,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>3556000</v>
       </c>
@@ -2757,7 +2784,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>3578323</v>
       </c>
@@ -2768,7 +2795,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>3580671</v>
       </c>
@@ -2779,7 +2806,7 @@
         <v>46073</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>3616123</v>
       </c>
@@ -2790,7 +2817,7 @@
         <v>46180</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>3626299</v>
       </c>
@@ -2801,7 +2828,7 @@
         <v>45939</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>3663021</v>
       </c>
@@ -2812,7 +2839,7 @@
         <v>46015</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>3669819</v>
       </c>
@@ -2823,7 +2850,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>3683605</v>
       </c>
@@ -2834,7 +2861,7 @@
         <v>45957</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>3690383</v>
       </c>
@@ -2845,7 +2872,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>3734971</v>
       </c>
@@ -2856,7 +2883,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>3778985</v>
       </c>
@@ -2867,7 +2894,7 @@
         <v>46186</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>3800136</v>
       </c>
@@ -2878,7 +2905,7 @@
         <v>46002</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>3800845</v>
       </c>
@@ -2889,7 +2916,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>3813424</v>
       </c>
@@ -2900,7 +2927,7 @@
         <v>45951</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>3830456</v>
       </c>
@@ -2911,7 +2938,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>3863582</v>
       </c>
@@ -2922,7 +2949,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>3870955</v>
       </c>
@@ -2933,7 +2960,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>3898698</v>
       </c>
@@ -2944,7 +2971,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>3909922</v>
       </c>
@@ -2955,7 +2982,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>3911458</v>
       </c>
@@ -2966,7 +2993,7 @@
         <v>45936</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>3944952</v>
       </c>
@@ -2977,7 +3004,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>3975438</v>
       </c>
@@ -2988,7 +3015,7 @@
         <v>46013</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>3988182</v>
       </c>
@@ -2999,7 +3026,7 @@
         <v>46229</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>4002781</v>
       </c>
@@ -3010,7 +3037,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>4008721</v>
       </c>
@@ -3021,7 +3048,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>4013049</v>
       </c>
@@ -3032,7 +3059,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>4015942</v>
       </c>
@@ -3043,7 +3070,7 @@
         <v>46211</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>4016083</v>
       </c>
@@ -3054,7 +3081,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>4019940</v>
       </c>
@@ -3065,7 +3092,7 @@
         <v>46021</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>4024143</v>
       </c>
@@ -3076,7 +3103,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>4025880</v>
       </c>
@@ -3087,7 +3114,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>4085242</v>
       </c>
@@ -3098,7 +3125,7 @@
         <v>45981</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>4098528</v>
       </c>
@@ -3109,7 +3136,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>4144969</v>
       </c>
@@ -3120,7 +3147,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>4148967</v>
       </c>
@@ -3131,7 +3158,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>4160521</v>
       </c>
@@ -3142,7 +3169,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>4168488</v>
       </c>
@@ -3153,7 +3180,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>4170786</v>
       </c>
@@ -3164,7 +3191,7 @@
         <v>46172</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>4192390</v>
       </c>
@@ -3175,7 +3202,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>4195067</v>
       </c>
@@ -3186,7 +3213,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>4195512</v>
       </c>
@@ -3197,7 +3224,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>4224945</v>
       </c>
@@ -3208,7 +3235,7 @@
         <v>46182</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>4224945</v>
       </c>
@@ -3219,7 +3246,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>4226975</v>
       </c>
@@ -3230,7 +3257,7 @@
         <v>46085</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>4230582</v>
       </c>
@@ -3241,7 +3268,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>4240824</v>
       </c>
@@ -3252,7 +3279,7 @@
         <v>45970</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>4244478</v>
       </c>
@@ -3263,7 +3290,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>4254025</v>
       </c>
@@ -3274,7 +3301,7 @@
         <v>45934</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>4254025</v>
       </c>
@@ -3285,7 +3312,7 @@
         <v>45957</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>4272910</v>
       </c>
@@ -3296,7 +3323,7 @@
         <v>46011</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>4274661</v>
       </c>
@@ -3307,7 +3334,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>4283545</v>
       </c>
@@ -3318,7 +3345,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>4291542</v>
       </c>
@@ -3329,7 +3356,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>4327424</v>
       </c>
@@ -3340,7 +3367,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>4327525</v>
       </c>
@@ -3351,7 +3378,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>4346791</v>
       </c>
@@ -3362,7 +3389,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>4348909</v>
       </c>
@@ -3373,7 +3400,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>4350067</v>
       </c>
@@ -3384,7 +3411,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>4391025</v>
       </c>
@@ -3395,7 +3422,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>4404567</v>
       </c>
@@ -3406,7 +3433,7 @@
         <v>45969</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>4408589</v>
       </c>
@@ -3417,7 +3444,7 @@
         <v>46214</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>4408969</v>
       </c>
@@ -3428,7 +3455,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>4409909</v>
       </c>
@@ -3439,7 +3466,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>4418883</v>
       </c>
@@ -3450,7 +3477,7 @@
         <v>46019</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>4427907</v>
       </c>
@@ -3461,7 +3488,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>4428163</v>
       </c>
@@ -3472,7 +3499,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>4442644</v>
       </c>
@@ -3483,7 +3510,7 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>4455350</v>
       </c>
@@ -3494,7 +3521,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>4484503</v>
       </c>
@@ -3505,7 +3532,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>4487357</v>
       </c>
@@ -3516,7 +3543,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>4515346</v>
       </c>
@@ -3527,7 +3554,7 @@
         <v>46009</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>4564438</v>
       </c>
@@ -3538,7 +3565,7 @@
         <v>45934</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>4583363</v>
       </c>
@@ -3549,7 +3576,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>4599354</v>
       </c>
@@ -3560,7 +3587,7 @@
         <v>45943</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>4605361</v>
       </c>
@@ -3571,7 +3598,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>4619601</v>
       </c>
@@ -3582,7 +3609,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>4622381</v>
       </c>
@@ -3593,7 +3620,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>4624450</v>
       </c>
@@ -3604,7 +3631,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>4691108</v>
       </c>
@@ -3615,7 +3642,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>4700591</v>
       </c>
@@ -3626,7 +3653,7 @@
         <v>46029</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>4704513</v>
       </c>
@@ -3637,7 +3664,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>4724414</v>
       </c>
@@ -3648,7 +3675,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>4727814</v>
       </c>
@@ -3659,7 +3686,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>4779015</v>
       </c>
@@ -3670,7 +3697,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>4779546</v>
       </c>
@@ -3681,7 +3708,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>4824290</v>
       </c>
@@ -3692,7 +3719,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>4834544</v>
       </c>
@@ -3703,7 +3730,7 @@
         <v>46060</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>4840840</v>
       </c>
@@ -3714,7 +3741,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>4855942</v>
       </c>
@@ -3725,7 +3752,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>4880197</v>
       </c>
@@ -3736,7 +3763,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>4903072</v>
       </c>
@@ -3747,7 +3774,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>4907602</v>
       </c>
@@ -3758,7 +3785,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>4919405</v>
       </c>
@@ -3769,7 +3796,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>4931425</v>
       </c>
@@ -3780,7 +3807,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>4934623</v>
       </c>
@@ -3791,7 +3818,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>4949523</v>
       </c>
@@ -3802,7 +3829,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>4963713</v>
       </c>
@@ -3813,7 +3840,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>5018610</v>
       </c>
@@ -3824,7 +3851,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>5039551</v>
       </c>
@@ -3835,7 +3862,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>5047065</v>
       </c>
@@ -3846,7 +3873,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>5053929</v>
       </c>
@@ -3857,7 +3884,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>5061750</v>
       </c>
@@ -3868,7 +3895,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>5072765</v>
       </c>
@@ -3879,7 +3906,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>5074517</v>
       </c>
@@ -3890,7 +3917,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>5097856</v>
       </c>
@@ -3901,7 +3928,7 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>5102102</v>
       </c>
@@ -3912,7 +3939,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>5129754</v>
       </c>
@@ -3923,7 +3950,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>5156915</v>
       </c>
@@ -3934,7 +3961,7 @@
         <v>45937</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>5160508</v>
       </c>
@@ -3945,7 +3972,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>5169479</v>
       </c>
@@ -3956,7 +3983,7 @@
         <v>45957</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>5181499</v>
       </c>
@@ -3967,7 +3994,7 @@
         <v>45983</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>5186336</v>
       </c>
@@ -3978,7 +4005,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>5188075</v>
       </c>
@@ -3989,7 +4016,7 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>5209603</v>
       </c>
@@ -4000,7 +4027,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>5218587</v>
       </c>
@@ -4011,7 +4038,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>5234935</v>
       </c>
@@ -4022,7 +4049,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>5239620</v>
       </c>
@@ -4033,7 +4060,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>5241120</v>
       </c>
@@ -4044,7 +4071,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>5257539</v>
       </c>
@@ -4055,7 +4082,7 @@
         <v>45995</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>5269180</v>
       </c>
@@ -4066,7 +4093,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>5287734</v>
       </c>
@@ -4077,7 +4104,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>5312032</v>
       </c>
@@ -4088,7 +4115,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>5326485</v>
       </c>
@@ -4099,7 +4126,7 @@
         <v>46106</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>5361162</v>
       </c>
@@ -4110,7 +4137,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>5370212</v>
       </c>
@@ -4121,7 +4148,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>5378345</v>
       </c>
@@ -4132,7 +4159,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>5380910</v>
       </c>
@@ -4143,7 +4170,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>5402689</v>
       </c>
@@ -4154,7 +4181,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>5404835</v>
       </c>
@@ -4165,7 +4192,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>5404924</v>
       </c>
@@ -4176,7 +4203,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>5427275</v>
       </c>
@@ -4187,7 +4214,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>5433913</v>
       </c>
@@ -4198,7 +4225,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>5471406</v>
       </c>
@@ -4209,7 +4236,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>5490608</v>
       </c>
@@ -4220,7 +4247,7 @@
         <v>45976</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>5490608</v>
       </c>
@@ -4231,7 +4258,7 @@
         <v>46012</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>5490711</v>
       </c>
@@ -4242,7 +4269,7 @@
         <v>46216</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>5501956</v>
       </c>
@@ -4253,7 +4280,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>5510765</v>
       </c>
@@ -4264,7 +4291,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>5513901</v>
       </c>
@@ -4275,7 +4302,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>5520881</v>
       </c>
@@ -4286,7 +4313,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>5557535</v>
       </c>
@@ -4297,7 +4324,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>5565188</v>
       </c>
@@ -4308,7 +4335,7 @@
         <v>46179</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>5570177</v>
       </c>
@@ -4319,7 +4346,7 @@
         <v>45983</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>5578553</v>
       </c>
@@ -4330,7 +4357,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>5594672</v>
       </c>
@@ -4341,7 +4368,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>5618472</v>
       </c>
@@ -4352,7 +4379,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>5621102</v>
       </c>
@@ -4363,7 +4390,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>5636254</v>
       </c>
@@ -4374,7 +4401,7 @@
         <v>46194</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>5655773</v>
       </c>
@@ -4385,7 +4412,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>5658298</v>
       </c>
@@ -4396,7 +4423,7 @@
         <v>46207</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>5666017</v>
       </c>
@@ -4407,7 +4434,7 @@
         <v>45988</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>5667425</v>
       </c>
@@ -4418,7 +4445,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>5672109</v>
       </c>
@@ -4429,7 +4456,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>5676208</v>
       </c>
@@ -4440,7 +4467,7 @@
         <v>46003</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>5717371</v>
       </c>
@@ -4451,7 +4478,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>5720897</v>
       </c>
@@ -4462,7 +4489,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>5727702</v>
       </c>
@@ -4473,7 +4500,7 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>5768695</v>
       </c>
@@ -4484,7 +4511,7 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>5776161</v>
       </c>
@@ -4495,7 +4522,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>5790907</v>
       </c>
@@ -4506,7 +4533,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>5815634</v>
       </c>
@@ -4517,7 +4544,7 @@
         <v>46233</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>5828643</v>
       </c>
@@ -4528,7 +4555,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>5830600</v>
       </c>
@@ -4539,7 +4566,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>5839557</v>
       </c>
@@ -4550,7 +4577,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>5839608</v>
       </c>
@@ -4561,7 +4588,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>5846590</v>
       </c>
@@ -4572,7 +4599,7 @@
         <v>46049</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>5855587</v>
       </c>
@@ -4583,7 +4610,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>5881986</v>
       </c>
@@ -4594,7 +4621,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>5889691</v>
       </c>
@@ -4605,7 +4632,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>5901601</v>
       </c>
@@ -4616,7 +4643,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>5902982</v>
       </c>
@@ -4627,7 +4654,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>5907778</v>
       </c>
@@ -4638,7 +4665,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>5917921</v>
       </c>
@@ -4649,7 +4676,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>5931870</v>
       </c>
@@ -4660,7 +4687,7 @@
         <v>46074</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>5938711</v>
       </c>
@@ -4671,7 +4698,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>5940780</v>
       </c>
@@ -4682,7 +4709,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>5941326</v>
       </c>
@@ -4693,7 +4720,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>5946403</v>
       </c>
@@ -4704,7 +4731,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>5952812</v>
       </c>
@@ -4715,7 +4742,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>5967130</v>
       </c>
@@ -4726,7 +4753,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>5971797</v>
       </c>
@@ -4737,7 +4764,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>5975050</v>
       </c>
@@ -4748,7 +4775,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>5999101</v>
       </c>
@@ -4759,7 +4786,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>6005145</v>
       </c>
@@ -4770,7 +4797,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>6011718</v>
       </c>
@@ -4781,7 +4808,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A400">
         <v>6017633</v>
       </c>
@@ -4792,7 +4819,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A401">
         <v>6020046</v>
       </c>
@@ -4803,7 +4830,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A402">
         <v>6027963</v>
       </c>
@@ -4814,7 +4841,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A403">
         <v>6031532</v>
       </c>
@@ -4825,7 +4852,7 @@
         <v>46207</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A404">
         <v>6037560</v>
       </c>
@@ -4836,7 +4863,7 @@
         <v>46107</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A405">
         <v>6045733</v>
       </c>
@@ -4847,7 +4874,7 @@
         <v>46130</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A406">
         <v>6047686</v>
       </c>
@@ -4858,7 +4885,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A407">
         <v>6051445</v>
       </c>
@@ -4869,7 +4896,7 @@
         <v>45990</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A408">
         <v>6064959</v>
       </c>
@@ -4880,7 +4907,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A409">
         <v>6070368</v>
       </c>
@@ -4891,7 +4918,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A410">
         <v>6072689</v>
       </c>
@@ -4902,7 +4929,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A411">
         <v>6088581</v>
       </c>
@@ -4913,7 +4940,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A412">
         <v>6119463</v>
       </c>
@@ -4924,7 +4951,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A413">
         <v>6137308</v>
       </c>
@@ -4935,7 +4962,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A414">
         <v>6138057</v>
       </c>
@@ -4946,7 +4973,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A415">
         <v>6138122</v>
       </c>
@@ -4957,7 +4984,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A416">
         <v>6154784</v>
       </c>
@@ -4968,7 +4995,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A417">
         <v>6171526</v>
       </c>
@@ -4979,7 +5006,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A418">
         <v>6177833</v>
       </c>
@@ -4990,7 +5017,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A419">
         <v>6178114</v>
       </c>
@@ -5001,7 +5028,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A420">
         <v>6185309</v>
       </c>
@@ -5012,7 +5039,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A421">
         <v>6192405</v>
       </c>
@@ -5023,7 +5050,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A422">
         <v>6201280</v>
       </c>
@@ -5034,7 +5061,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A423">
         <v>6214465</v>
       </c>
@@ -5045,7 +5072,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A424">
         <v>6228072</v>
       </c>
@@ -5056,7 +5083,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A425">
         <v>6260056</v>
       </c>
@@ -5067,7 +5094,7 @@
         <v>45966</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A426">
         <v>6262947</v>
       </c>
@@ -5078,7 +5105,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A427">
         <v>6267062</v>
       </c>
@@ -5089,7 +5116,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A428">
         <v>6272176</v>
       </c>
@@ -5100,7 +5127,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A429">
         <v>6299982</v>
       </c>
@@ -5111,7 +5138,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A430">
         <v>6300230</v>
       </c>
@@ -5122,7 +5149,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A431">
         <v>6314809</v>
       </c>
@@ -5133,7 +5160,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A432">
         <v>6315964</v>
       </c>
@@ -5144,7 +5171,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A433">
         <v>6316473</v>
       </c>
@@ -5155,7 +5182,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A434">
         <v>6317160</v>
       </c>
@@ -5166,7 +5193,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A435">
         <v>6321905</v>
       </c>
@@ -5177,7 +5204,7 @@
         <v>46005</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A436">
         <v>6321905</v>
       </c>
@@ -5188,7 +5215,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A437">
         <v>6341313</v>
       </c>
@@ -5199,7 +5226,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A438">
         <v>6343646</v>
       </c>
@@ -5210,7 +5237,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A439">
         <v>6345878</v>
       </c>
@@ -5221,7 +5248,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A440">
         <v>6351201</v>
       </c>
@@ -5232,7 +5259,7 @@
         <v>45971</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A441">
         <v>6362343</v>
       </c>
@@ -5243,7 +5270,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A442">
         <v>6362343</v>
       </c>
@@ -5254,7 +5281,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A443">
         <v>6414091</v>
       </c>
@@ -5265,7 +5292,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A444">
         <v>6417908</v>
       </c>
@@ -5276,7 +5303,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A445">
         <v>6419786</v>
       </c>
@@ -5287,7 +5314,7 @@
         <v>45991</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A446">
         <v>6426109</v>
       </c>
@@ -5298,7 +5325,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A447">
         <v>6439980</v>
       </c>
@@ -5309,7 +5336,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A448">
         <v>6464527</v>
       </c>
@@ -5320,7 +5347,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A449">
         <v>6468260</v>
       </c>
@@ -5331,7 +5358,7 @@
         <v>45952</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A450">
         <v>6476508</v>
       </c>
@@ -5342,7 +5369,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A451">
         <v>6479453</v>
       </c>
@@ -5353,7 +5380,7 @@
         <v>45948</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A452">
         <v>6507327</v>
       </c>
@@ -5364,7 +5391,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A453">
         <v>6523319</v>
       </c>
@@ -5375,7 +5402,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A454">
         <v>6526670</v>
       </c>
@@ -5386,7 +5413,7 @@
         <v>45981</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A455">
         <v>6526733</v>
       </c>
@@ -5397,7 +5424,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A456">
         <v>6531075</v>
       </c>
@@ -5408,7 +5435,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A457">
         <v>6562424</v>
       </c>
@@ -5419,7 +5446,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A458">
         <v>6563589</v>
       </c>
@@ -5430,7 +5457,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A459">
         <v>6563589</v>
       </c>
@@ -5441,7 +5468,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A460">
         <v>6565420</v>
       </c>
@@ -5452,7 +5479,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A461">
         <v>6583050</v>
       </c>
@@ -5463,7 +5490,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A462">
         <v>6601531</v>
       </c>
@@ -5474,7 +5501,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A463">
         <v>6604020</v>
       </c>
@@ -5485,7 +5512,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A464">
         <v>6604020</v>
       </c>
@@ -5496,7 +5523,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A465">
         <v>6615770</v>
       </c>
@@ -5507,7 +5534,7 @@
         <v>46109</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A466">
         <v>6618637</v>
       </c>
@@ -5518,7 +5545,7 @@
         <v>46057</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A467">
         <v>6619968</v>
       </c>
@@ -5529,7 +5556,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A468">
         <v>6630099</v>
       </c>
@@ -5540,7 +5567,7 @@
         <v>45955</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A469">
         <v>6644947</v>
       </c>
@@ -5551,7 +5578,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A470">
         <v>6661525</v>
       </c>
@@ -5562,7 +5589,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A471">
         <v>6665016</v>
       </c>
@@ -5573,7 +5600,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A472">
         <v>6666323</v>
       </c>
@@ -5584,7 +5611,7 @@
         <v>46091</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A473">
         <v>6668290</v>
       </c>
@@ -5595,7 +5622,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A474">
         <v>6668466</v>
       </c>
@@ -5606,7 +5633,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A475">
         <v>6681058</v>
       </c>
@@ -5617,7 +5644,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A476">
         <v>6692176</v>
       </c>
@@ -5628,7 +5655,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A477">
         <v>6693180</v>
       </c>
@@ -5639,7 +5666,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A478">
         <v>6705226</v>
       </c>
@@ -5650,7 +5677,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A479">
         <v>6716596</v>
       </c>
@@ -5661,7 +5688,7 @@
         <v>46210</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A480">
         <v>6717841</v>
       </c>
@@ -5672,7 +5699,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A481">
         <v>6720747</v>
       </c>
@@ -5683,7 +5710,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A482">
         <v>6725672</v>
       </c>
@@ -5694,7 +5721,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A483">
         <v>6732514</v>
       </c>
@@ -5705,7 +5732,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A484">
         <v>6732716</v>
       </c>
@@ -5716,7 +5743,7 @@
         <v>45994</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A485">
         <v>6738530</v>
       </c>
@@ -5727,7 +5754,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A486">
         <v>6744470</v>
       </c>
@@ -5738,7 +5765,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A487">
         <v>6750803</v>
       </c>
@@ -5749,7 +5776,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A488">
         <v>6751413</v>
       </c>
@@ -5760,7 +5787,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A489">
         <v>6753847</v>
       </c>
@@ -5771,7 +5798,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A490">
         <v>6759952</v>
       </c>
@@ -5782,7 +5809,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A491">
         <v>6768418</v>
       </c>
@@ -5793,7 +5820,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A492">
         <v>6771996</v>
       </c>
@@ -5804,7 +5831,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A493">
         <v>6773611</v>
       </c>
@@ -5815,7 +5842,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A494">
         <v>6780503</v>
       </c>
@@ -5826,7 +5853,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A495">
         <v>6781404</v>
       </c>
@@ -5837,7 +5864,7 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A496">
         <v>6781719</v>
       </c>
@@ -5848,7 +5875,7 @@
         <v>46158</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A497">
         <v>6782456</v>
       </c>
@@ -5859,7 +5886,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A498">
         <v>6783321</v>
       </c>
@@ -5870,7 +5897,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A499">
         <v>6783496</v>
       </c>
@@ -5881,7 +5908,7 @@
         <v>46211</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A500">
         <v>6784260</v>
       </c>
@@ -5892,7 +5919,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A501">
         <v>6788775</v>
       </c>
@@ -5903,7 +5930,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A502">
         <v>6799615</v>
       </c>
@@ -5914,7 +5941,7 @@
         <v>46191</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A503">
         <v>6809834</v>
       </c>
@@ -5925,7 +5952,7 @@
         <v>45935</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A504">
         <v>6815407</v>
       </c>
@@ -5936,7 +5963,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A505">
         <v>6817792</v>
       </c>
@@ -5947,7 +5974,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A506">
         <v>6817792</v>
       </c>
@@ -5958,7 +5985,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A507">
         <v>6819455</v>
       </c>
@@ -5969,7 +5996,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A508">
         <v>6823288</v>
       </c>
@@ -5980,7 +6007,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A509">
         <v>6840551</v>
       </c>
@@ -5991,7 +6018,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A510">
         <v>6840664</v>
       </c>
@@ -6002,7 +6029,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A511">
         <v>6841363</v>
       </c>
@@ -6013,7 +6040,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A512">
         <v>6842466</v>
       </c>
@@ -6024,7 +6051,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A513">
         <v>6842466</v>
       </c>
@@ -6035,7 +6062,7 @@
         <v>46135</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A514">
         <v>6864296</v>
       </c>
@@ -6046,7 +6073,7 @@
         <v>45955</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A515">
         <v>6867292</v>
       </c>
@@ -6057,7 +6084,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A516">
         <v>6874463</v>
       </c>
@@ -6068,7 +6095,7 @@
         <v>46098</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A517">
         <v>6880151</v>
       </c>
@@ -6079,7 +6106,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A518">
         <v>6880719</v>
       </c>
@@ -6090,7 +6117,7 @@
         <v>46196</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A519">
         <v>6892738</v>
       </c>
@@ -6101,7 +6128,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A520">
         <v>6895900</v>
       </c>
@@ -6112,7 +6139,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A521">
         <v>6899225</v>
       </c>
@@ -6123,7 +6150,7 @@
         <v>45951</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A522">
         <v>6900939</v>
       </c>
@@ -6134,7 +6161,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A523">
         <v>6903872</v>
       </c>
@@ -6145,7 +6172,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A524">
         <v>6903872</v>
       </c>
@@ -6156,7 +6183,7 @@
         <v>46228</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A525">
         <v>6906448</v>
       </c>
@@ -6167,7 +6194,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A526">
         <v>6909329</v>
       </c>
@@ -6178,7 +6205,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A527">
         <v>6911348</v>
       </c>
@@ -6189,7 +6216,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A528">
         <v>6912376</v>
       </c>
@@ -6200,7 +6227,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A529">
         <v>6921971</v>
       </c>
@@ -6211,7 +6238,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A530">
         <v>6927808</v>
       </c>
@@ -6222,7 +6249,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A531">
         <v>6930918</v>
       </c>
@@ -6233,7 +6260,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A532">
         <v>6931009</v>
       </c>
@@ -6244,7 +6271,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A533">
         <v>6932897</v>
       </c>
@@ -6255,7 +6282,7 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A534">
         <v>6935401</v>
       </c>
@@ -6266,7 +6293,7 @@
         <v>46006</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A535">
         <v>6935475</v>
       </c>
@@ -6277,7 +6304,7 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A536">
         <v>6935475</v>
       </c>
@@ -6288,7 +6315,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A537">
         <v>6939839</v>
       </c>
@@ -6299,7 +6326,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A538">
         <v>6940387</v>
       </c>
@@ -6310,7 +6337,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A539">
         <v>6941303</v>
       </c>
@@ -6321,7 +6348,7 @@
         <v>45933</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A540">
         <v>6941719</v>
       </c>
@@ -6332,7 +6359,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A541">
         <v>6941846</v>
       </c>
@@ -6343,7 +6370,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A542">
         <v>6943078</v>
       </c>
@@ -6354,7 +6381,7 @@
         <v>45951</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A543">
         <v>6943307</v>
       </c>
@@ -6365,7 +6392,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A544">
         <v>6943496</v>
       </c>
@@ -6376,7 +6403,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A545">
         <v>6945212</v>
       </c>
@@ -6387,7 +6414,7 @@
         <v>45941</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A546">
         <v>6946430</v>
       </c>
@@ -6398,7 +6425,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A547">
         <v>6946492</v>
       </c>
@@ -6409,7 +6436,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A548">
         <v>6946858</v>
       </c>
@@ -6420,7 +6447,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A549">
         <v>6946911</v>
       </c>
@@ -6431,7 +6458,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A550">
         <v>6946997</v>
       </c>
@@ -6442,7 +6469,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A551">
         <v>6947139</v>
       </c>
@@ -6453,7 +6480,7 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A552">
         <v>6947228</v>
       </c>
@@ -6464,7 +6491,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A553">
         <v>6947456</v>
       </c>
@@ -6475,7 +6502,7 @@
         <v>45935</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A554">
         <v>6948446</v>
       </c>
@@ -6486,7 +6513,7 @@
         <v>45980</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A555">
         <v>6948662</v>
       </c>
@@ -6497,7 +6524,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A556">
         <v>6949400</v>
       </c>
@@ -6508,7 +6535,7 @@
         <v>45960</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A557">
         <v>6949676</v>
       </c>
@@ -6519,7 +6546,7 @@
         <v>45958</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A558">
         <v>6950427</v>
       </c>
@@ -6530,7 +6557,7 @@
         <v>45976</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A559">
         <v>6950819</v>
       </c>
@@ -6541,7 +6568,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A560">
         <v>6950857</v>
       </c>
@@ -6552,7 +6579,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A561">
         <v>6950960</v>
       </c>
@@ -6563,7 +6590,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A562">
         <v>6951176</v>
       </c>
@@ -6574,7 +6601,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A563">
         <v>6951316</v>
       </c>
@@ -6585,7 +6612,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A564">
         <v>6951556</v>
       </c>
@@ -6596,7 +6623,7 @@
         <v>45953</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A565">
         <v>6951722</v>
       </c>
@@ -6607,7 +6634,7 @@
         <v>45957</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A566">
         <v>6951948</v>
       </c>
@@ -6618,7 +6645,7 @@
         <v>45959</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A567">
         <v>6952217</v>
       </c>
@@ -6629,7 +6656,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A568">
         <v>6952229</v>
       </c>
@@ -6640,7 +6667,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A569">
         <v>6952750</v>
       </c>
@@ -6651,7 +6678,7 @@
         <v>46121</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A570">
         <v>6953233</v>
       </c>
@@ -6662,7 +6689,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A571">
         <v>6953447</v>
       </c>
@@ -6673,7 +6700,7 @@
         <v>45987</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A572">
         <v>6953447</v>
       </c>
@@ -6684,7 +6711,7 @@
         <v>46036</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A573">
         <v>6953447</v>
       </c>
@@ -6695,7 +6722,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A574">
         <v>6953877</v>
       </c>
@@ -6706,7 +6733,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A575">
         <v>6955807</v>
       </c>
@@ -6717,7 +6744,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A576">
         <v>6955807</v>
       </c>
@@ -6728,7 +6755,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A577">
         <v>6955946</v>
       </c>
@@ -6739,7 +6766,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A578">
         <v>6956001</v>
       </c>
@@ -6750,7 +6777,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A579">
         <v>6957229</v>
       </c>
@@ -6761,7 +6788,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A580">
         <v>6957801</v>
       </c>
@@ -6772,7 +6799,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A581">
         <v>6959071</v>
       </c>
@@ -6783,7 +6810,7 @@
         <v>46021</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A582">
         <v>6960163</v>
       </c>
@@ -6794,7 +6821,7 @@
         <v>45982</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A583">
         <v>6960339</v>
       </c>
@@ -6805,7 +6832,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A584">
         <v>6960682</v>
       </c>
@@ -6816,7 +6843,7 @@
         <v>45983</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A585">
         <v>6960860</v>
       </c>
@@ -6827,7 +6854,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A586">
         <v>6960909</v>
       </c>
@@ -6838,7 +6865,7 @@
         <v>45997</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A587">
         <v>6960959</v>
       </c>
@@ -6849,7 +6876,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A588">
         <v>6961216</v>
       </c>
@@ -6860,7 +6887,7 @@
         <v>46018</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A589">
         <v>6961292</v>
       </c>
@@ -6871,7 +6898,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A590">
         <v>6961622</v>
       </c>
@@ -6882,7 +6909,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A591">
         <v>6962674</v>
       </c>
@@ -6893,7 +6920,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A592">
         <v>6962751</v>
       </c>
@@ -6904,7 +6931,7 @@
         <v>46019</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A593">
         <v>6962941</v>
       </c>
@@ -6915,7 +6942,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A594">
         <v>6963107</v>
       </c>
@@ -6926,7 +6953,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A595">
         <v>6963525</v>
       </c>
@@ -6937,7 +6964,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A596">
         <v>6964173</v>
       </c>
@@ -6948,7 +6975,7 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A597">
         <v>6964616</v>
       </c>
@@ -6959,7 +6986,7 @@
         <v>46017</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A598">
         <v>6964630</v>
       </c>
@@ -6970,7 +6997,7 @@
         <v>46014</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A599">
         <v>6964692</v>
       </c>
@@ -6981,7 +7008,7 @@
         <v>46211</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A600">
         <v>6964907</v>
       </c>
@@ -6992,7 +7019,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A601">
         <v>6965389</v>
       </c>
@@ -7003,7 +7030,7 @@
         <v>46083</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A602">
         <v>6965416</v>
       </c>
@@ -7014,7 +7041,7 @@
         <v>46016</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A603">
         <v>6966038</v>
       </c>
@@ -7025,7 +7052,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A604">
         <v>6966242</v>
       </c>
@@ -7036,7 +7063,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A605">
         <v>6967129</v>
       </c>
@@ -7047,7 +7074,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A606">
         <v>6967270</v>
       </c>
@@ -7058,7 +7085,7 @@
         <v>46031</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A607">
         <v>6967333</v>
       </c>
@@ -7069,7 +7096,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A608">
         <v>6967749</v>
       </c>
@@ -7080,7 +7107,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A609">
         <v>6968094</v>
       </c>
@@ -7091,7 +7118,7 @@
         <v>46037</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A610">
         <v>6968183</v>
       </c>
@@ -7102,7 +7129,7 @@
         <v>46051</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A611">
         <v>6970037</v>
       </c>
@@ -7113,7 +7140,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A612">
         <v>6970075</v>
       </c>
@@ -7124,7 +7151,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A613">
         <v>6970227</v>
       </c>
@@ -7135,7 +7162,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A614">
         <v>6970328</v>
       </c>
@@ -7146,7 +7173,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A615">
         <v>6970354</v>
       </c>
@@ -7157,7 +7184,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A616">
         <v>6971510</v>
       </c>
@@ -7168,7 +7195,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A617">
         <v>6972029</v>
       </c>
@@ -7179,7 +7206,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A618">
         <v>6972372</v>
       </c>
@@ -7190,7 +7217,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A619">
         <v>6973956</v>
       </c>
@@ -7201,7 +7228,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A620">
         <v>6974415</v>
       </c>
@@ -7212,7 +7239,7 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A621">
         <v>6974794</v>
       </c>
@@ -7223,7 +7250,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A622">
         <v>6975075</v>
       </c>
@@ -7234,7 +7261,7 @@
         <v>46058</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A623">
         <v>6976320</v>
       </c>
@@ -7245,7 +7272,7 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A624">
         <v>6977079</v>
       </c>
@@ -7256,7 +7283,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A625">
         <v>6977257</v>
       </c>
@@ -7267,7 +7294,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A626">
         <v>6977790</v>
       </c>
@@ -7278,7 +7305,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A627">
         <v>6979112</v>
       </c>
@@ -7289,7 +7316,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A628">
         <v>6979314</v>
       </c>
@@ -7300,7 +7327,7 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A629">
         <v>6979477</v>
       </c>
@@ -7311,7 +7338,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A630">
         <v>6980292</v>
       </c>
@@ -7322,7 +7349,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A631">
         <v>6980367</v>
       </c>
@@ -7333,7 +7360,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A632">
         <v>6980519</v>
       </c>
@@ -7344,7 +7371,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A633">
         <v>6980711</v>
       </c>
@@ -7355,7 +7382,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A634">
         <v>6981585</v>
       </c>
@@ -7366,7 +7393,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A635">
         <v>6981953</v>
       </c>
@@ -7377,7 +7404,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A636">
         <v>6982272</v>
       </c>
@@ -7388,7 +7415,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A637">
         <v>6982842</v>
       </c>
@@ -7399,7 +7426,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A638">
         <v>6982854</v>
       </c>
@@ -7410,7 +7437,7 @@
         <v>46092</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A639">
         <v>6983084</v>
       </c>
@@ -7421,7 +7448,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A640">
         <v>6984290</v>
       </c>
@@ -7432,7 +7459,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A641">
         <v>6984416</v>
       </c>
@@ -7443,7 +7470,7 @@
         <v>46115</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A642">
         <v>6984466</v>
       </c>
@@ -7454,7 +7481,7 @@
         <v>46105</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A643">
         <v>6984505</v>
       </c>
@@ -7465,7 +7492,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A644">
         <v>6984973</v>
       </c>
@@ -7476,7 +7503,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A645">
         <v>6984985</v>
       </c>
@@ -7487,7 +7514,7 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A646">
         <v>6986915</v>
       </c>
@@ -7498,7 +7525,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A647">
         <v>6987501</v>
       </c>
@@ -7509,7 +7536,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A648">
         <v>6987537</v>
       </c>
@@ -7520,7 +7547,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A649">
         <v>6987777</v>
       </c>
@@ -7531,7 +7558,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A650">
         <v>6988399</v>
       </c>
@@ -7542,7 +7569,7 @@
         <v>46136</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A651">
         <v>6989517</v>
       </c>
@@ -7553,7 +7580,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A652">
         <v>6992564</v>
       </c>
@@ -7564,7 +7591,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A653">
         <v>6992766</v>
       </c>
@@ -7575,7 +7602,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A654">
         <v>6992906</v>
       </c>
@@ -7586,7 +7613,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A655">
         <v>6994710</v>
       </c>
@@ -7597,7 +7624,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A656">
         <v>6994772</v>
       </c>
@@ -7608,7 +7635,7 @@
         <v>46154</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A657">
         <v>6995469</v>
       </c>
@@ -7619,7 +7646,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A658">
         <v>6995902</v>
       </c>
@@ -7630,7 +7657,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A659">
         <v>6995926</v>
       </c>
@@ -7641,7 +7668,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A660">
         <v>6996651</v>
       </c>
@@ -7652,7 +7679,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A661">
         <v>6997033</v>
       </c>
@@ -7663,7 +7690,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A662">
         <v>6997045</v>
       </c>
@@ -7674,7 +7701,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A663">
         <v>6997057</v>
       </c>
@@ -7685,7 +7712,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A664">
         <v>6997071</v>
       </c>
@@ -7696,7 +7723,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A665">
         <v>6997603</v>
       </c>
@@ -7707,7 +7734,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A666">
         <v>6997944</v>
       </c>
@@ -7718,7 +7745,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A667">
         <v>6998198</v>
       </c>
@@ -7729,7 +7756,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A668">
         <v>6998388</v>
       </c>
@@ -7740,7 +7767,7 @@
         <v>46209</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A669">
         <v>6999784</v>
       </c>
@@ -7751,7 +7778,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A670">
         <v>6999809</v>
       </c>
@@ -7762,7 +7789,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A671">
         <v>7001768</v>
       </c>
@@ -7773,7 +7800,7 @@
         <v>46211</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A672">
         <v>7002013</v>
       </c>
@@ -7784,7 +7811,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A673">
         <v>7002291</v>
       </c>
@@ -7795,7 +7822,7 @@
         <v>46216</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A674">
         <v>7002342</v>
       </c>
@@ -7806,7 +7833,7 @@
         <v>46216</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A675">
         <v>7002912</v>
       </c>
@@ -7817,7 +7844,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A676">
         <v>7003229</v>
       </c>
@@ -7828,7 +7855,7 @@
         <v>46189</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A677">
         <v>7005855</v>
       </c>
@@ -7839,7 +7866,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A678">
         <v>7006972</v>
       </c>
@@ -7850,7 +7877,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A679">
         <v>7007241</v>
       </c>
@@ -7861,7 +7888,7 @@
         <v>46205</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A680">
         <v>7007645</v>
       </c>
@@ -7872,7 +7899,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A681">
         <v>7007760</v>
       </c>
@@ -7883,7 +7910,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A682">
         <v>7008445</v>
       </c>
@@ -7894,7 +7921,7 @@
         <v>46211</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A683">
         <v>7010022</v>
       </c>
@@ -7905,7 +7932,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A684">
         <v>7011062</v>
       </c>
@@ -7916,7 +7943,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A685">
         <v>7011214</v>
       </c>
@@ -7927,7 +7954,7 @@
         <v>46226</v>
       </c>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A686">
         <v>7011341</v>
       </c>
@@ -7938,7 +7965,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A687">
         <v>7011745</v>
       </c>
@@ -7949,7 +7976,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A688">
         <v>7011769</v>
       </c>
@@ -7960,7 +7987,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A689">
         <v>7012242</v>
       </c>
@@ -7971,7 +7998,7 @@
         <v>46225</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A690">
         <v>7012278</v>
       </c>
@@ -7982,7 +8009,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A691">
         <v>7013787</v>
       </c>
@@ -7993,7 +8020,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A692">
         <v>7014412</v>
       </c>
